--- a/www/flightdata/xlsx/eoss-319.xlsx
+++ b/www/flightdata/xlsx/eoss-319.xlsx
@@ -3528,7 +3528,7 @@
         <v>29202.89</v>
       </c>
       <c r="I2">
-        <v>609</v>
+        <v>451</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
